--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N53_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N53_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>12.16552506059644</v>
+        <v>1.976897822346921</v>
       </c>
       <c r="D2" t="n">
-        <v>28.37706625253352</v>
+        <v>4.611273266036697</v>
       </c>
       <c r="E2" t="n">
-        <v>27.18924147669381</v>
+        <v>4.418251739962744</v>
       </c>
       <c r="F2" t="n">
-        <v>23.44747902816766</v>
+        <v>3.810215342077244</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>78.44630726137477</v>
+        <v>12.7475249299734</v>
       </c>
       <c r="D3" t="n">
-        <v>79.02672643966804</v>
+        <v>12.84184304644606</v>
       </c>
       <c r="E3" t="n">
-        <v>27.18924147669381</v>
+        <v>4.418251739962744</v>
       </c>
       <c r="F3" t="n">
-        <v>23.44747902816766</v>
+        <v>3.810215342077244</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>37.78145541770504</v>
+        <v>6.139486505377069</v>
       </c>
       <c r="D4" t="n">
-        <v>46.16635645014203</v>
+        <v>7.50203292314808</v>
       </c>
       <c r="E4" t="n">
-        <v>27.18924147669381</v>
+        <v>4.418251739962744</v>
       </c>
       <c r="F4" t="n">
-        <v>23.44747902816766</v>
+        <v>3.810215342077244</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>77.84699828304608</v>
+        <v>12.65013722099499</v>
       </c>
       <c r="D5" t="n">
-        <v>78.43391058815617</v>
+        <v>12.74551047057538</v>
       </c>
       <c r="E5" t="n">
-        <v>27.18924147669381</v>
+        <v>4.418251739962744</v>
       </c>
       <c r="F5" t="n">
-        <v>23.44747902816766</v>
+        <v>3.810215342077244</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>25.56436231726883</v>
+        <v>4.154208876556186</v>
       </c>
       <c r="D6" t="n">
-        <v>24.99154436286111</v>
+        <v>4.06112595896493</v>
       </c>
       <c r="E6" t="n">
-        <v>27.18924147669381</v>
+        <v>4.418251739962744</v>
       </c>
       <c r="F6" t="n">
-        <v>23.44747902816766</v>
+        <v>3.810215342077244</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
